--- a/output/2026-10-10_17_Serbia_Podunavski_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-10_17_Serbia_Podunavski_Utensilerie_e_Macchine_Utensili.xlsx
@@ -474,7 +474,6 @@
           <t>Woby Haus - prodaja mašina i alata</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Smederevo, Podunavski okrug</t>
@@ -490,10 +489,9 @@
           <t>026/463-2144</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato su planplus.rs (Despota Đurđa 15, orari Lun-Sab 07:00-20:00). Sito web non confermabile con fonte reale, lasciato vuoto.</t>
+          <t>Verificato su planplus.rs (Despota Đurđa 15, orari Lun-Sab 07:00-20:00). Sito web non confermabile con fonte reale, lasciato vuoto. [DUPLICATO — vedi anche: 2026-10-08_01_Serbia_Kolubarski_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -508,7 +506,6 @@
           <t>Robna kuća Tri O (filiale Smederevo)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Smederevo, Podunavski okrug</t>
@@ -524,7 +521,6 @@
           <t>026/613-060</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Azienda TRI O d.o.o. confermata (profilo eponuda.com: 30+ anni attività, 25 punti vendita incl. Smederevo).</t>
@@ -542,7 +538,6 @@
           <t>Robna kuća Tri O (filiale Velika Plana)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Velika Plana, Podunavski okrug</t>
@@ -558,7 +553,6 @@
           <t>026/513-292</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Indirizzo e telefono confermati via fetch diretto su planplus.rs/velika-plana/kucni-aparati (Kralja Petra I 44).</t>
